--- a/data/trans_camb/P74B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 8,52</t>
+          <t>-4,7; 9,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 15,25</t>
+          <t>0,54; 15,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -9,54</t>
+          <t>-54,07; -8,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-49,84; -7,37</t>
+          <t>-50,03; -7,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 9,74</t>
+          <t>-7,03; 9,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 17,07</t>
+          <t>-0,65; 16,96</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 184,24</t>
+          <t>-48,25; 204,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 308,75</t>
+          <t>-0,36; 344,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,27; -12,37</t>
+          <t>-59,75; -12,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,44; -10,81</t>
+          <t>-56,0; -10,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 76,78</t>
+          <t>-33,55; 69,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 131,97</t>
+          <t>-5,4; 126,97</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 12,83</t>
+          <t>-1,7; 12,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 14,6</t>
+          <t>0,57; 14,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 13,07</t>
+          <t>-39,26; 14,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-54,45; 1,56</t>
+          <t>-51,8; 3,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 14,6</t>
+          <t>-1,27; 15,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 13,97</t>
+          <t>-2,43; 13,8</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 358,99</t>
+          <t>-25,38; 319,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 377,79</t>
+          <t>-1,28; 394,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,09; 26,43</t>
+          <t>-48,04; 25,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 0,8</t>
+          <t>-62,54; 6,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 144,73</t>
+          <t>-7,85; 158,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 135,89</t>
+          <t>-13,84; 140,13</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,35</t>
+          <t>4,43; 14,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,47</t>
+          <t>4,37; 13,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 5,23</t>
+          <t>-32,51; 5,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 8,94</t>
+          <t>-31,38; 7,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 16,86</t>
+          <t>5,78; 17,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 15,75</t>
+          <t>4,48; 16,02</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,7; 577,27</t>
+          <t>71,0; 582,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,56; 555,44</t>
+          <t>52,45; 550,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 8,11</t>
+          <t>-37,84; 7,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 14,04</t>
+          <t>-35,99; 10,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,24; 196,93</t>
+          <t>45,0; 207,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,46; 188,62</t>
+          <t>31,44; 189,07</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,52</t>
+          <t>-0,74; 5,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,94</t>
+          <t>-1,7; 5,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-37,47; -15,6</t>
+          <t>-37,66; -14,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-31,8; -11,3</t>
+          <t>-32,88; -9,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,8</t>
+          <t>-3,02; 5,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 6,01</t>
+          <t>-2,36; 5,66</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 83,41</t>
+          <t>-7,53; 76,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 65,17</t>
+          <t>-17,41; 65,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,95; -21,94</t>
+          <t>-46,99; -21,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,13; -16,1</t>
+          <t>-41,01; -13,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 33,89</t>
+          <t>-14,7; 32,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 35,4</t>
+          <t>-11,85; 32,98</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 16,66</t>
+          <t>3,18; 16,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 11,69</t>
+          <t>0,12; 11,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,06; -2,84</t>
+          <t>-23,85; -3,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-33,62; -11,14</t>
+          <t>-32,97; -12,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 14,62</t>
+          <t>-0,55; 14,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 3,32</t>
+          <t>-10,41; 4,39</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27,04; 378,13</t>
+          <t>26,28; 335,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 254,48</t>
+          <t>-2,73; 247,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,15; -4,77</t>
+          <t>-30,14; -5,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,62; -17,36</t>
+          <t>-41,09; -18,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 46,69</t>
+          <t>-2,18; 45,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 10,94</t>
+          <t>-25,88; 14,16</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 2,8</t>
+          <t>-6,89; 3,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 1,66</t>
+          <t>-9,0; 1,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 2,84</t>
+          <t>-7,25; 2,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 0,42</t>
+          <t>-10,14; 0,06</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 3,21</t>
+          <t>-7,6; 3,57</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 1,83</t>
+          <t>-9,94; 1,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 3,33</t>
+          <t>-8,02; 3,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 0,39</t>
+          <t>-11,12; 0,07</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,53</t>
+          <t>2,86; 7,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,33</t>
+          <t>2,74; 7,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,37; -10,49</t>
+          <t>-19,71; -10,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-21,45; -12,3</t>
+          <t>-21,44; -12,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,42</t>
+          <t>1,53; 7,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,47</t>
+          <t>0,57; 6,35</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>34,46; 117,92</t>
+          <t>33,17; 115,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>29,94; 112,36</t>
+          <t>29,57; 111,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,9; -12,91</t>
+          <t>-23,26; -13,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -15,37</t>
+          <t>-25,23; -15,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,94; 26,13</t>
+          <t>4,76; 24,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,2; 22,53</t>
+          <t>1,81; 22,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P74B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 9,04</t>
+          <t>-4,6; 8,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 15,3</t>
+          <t>0,14; 15,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-54,07; -8,79</t>
+          <t>-51,61; -9,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,03; -7,52</t>
+          <t>-49,34; -7,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 9,29</t>
+          <t>-6,17; 9,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 16,96</t>
+          <t>-0,76; 16,56</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 204,18</t>
+          <t>-50,25; 187,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 344,17</t>
+          <t>-5,46; 322,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,75; -12,53</t>
+          <t>-59,07; -14,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,0; -10,82</t>
+          <t>-55,09; -11,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 69,58</t>
+          <t>-31,68; 71,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 126,97</t>
+          <t>-4,45; 122,48</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 12,08</t>
+          <t>-1,17; 12,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 14,47</t>
+          <t>0,95; 15,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 14,11</t>
+          <t>-40,08; 13,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 3,94</t>
+          <t>-51,87; -0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 15,29</t>
+          <t>-1,23; 15,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 13,8</t>
+          <t>-2,01; 13,67</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 319,48</t>
+          <t>-20,75; 336,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 394,85</t>
+          <t>-0,8; 395,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 25,22</t>
+          <t>-47,8; 23,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,54; 6,21</t>
+          <t>-64,73; -3,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 158,76</t>
+          <t>-8,02; 169,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 140,13</t>
+          <t>-11,59; 143,47</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 14,16</t>
+          <t>4,82; 14,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 13,6</t>
+          <t>4,25; 13,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 5,88</t>
+          <t>-32,49; 5,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 7,33</t>
+          <t>-32,11; 9,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 17,15</t>
+          <t>4,91; 16,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 16,02</t>
+          <t>3,81; 15,81</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,0; 582,28</t>
+          <t>75,84; 563,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,45; 550,94</t>
+          <t>63,46; 564,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 7,86</t>
+          <t>-37,61; 7,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 10,0</t>
+          <t>-36,35; 13,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,0; 207,79</t>
+          <t>35,07; 203,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,44; 189,07</t>
+          <t>26,87; 195,66</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,99</t>
+          <t>-0,96; 6,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 5,19</t>
+          <t>-1,78; 5,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-37,66; -14,25</t>
+          <t>-37,31; -14,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-32,88; -9,46</t>
+          <t>-32,54; -10,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,7</t>
+          <t>-2,91; 5,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 5,66</t>
+          <t>-2,8; 5,93</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 76,89</t>
+          <t>-9,38; 86,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 65,02</t>
+          <t>-16,74; 68,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,99; -21,16</t>
+          <t>-46,84; -20,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,01; -13,0</t>
+          <t>-40,87; -14,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 32,37</t>
+          <t>-13,93; 33,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 32,98</t>
+          <t>-12,65; 34,7</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 16,29</t>
+          <t>1,97; 15,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 11,91</t>
+          <t>-0,29; 11,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,85; -3,56</t>
+          <t>-24,33; -3,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -12,09</t>
+          <t>-34,14; -13,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 14,45</t>
+          <t>-1,07; 14,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 4,39</t>
+          <t>-10,75; 3,36</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26,28; 335,86</t>
+          <t>11,44; 312,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 247,72</t>
+          <t>-5,68; 226,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,14; -5,38</t>
+          <t>-29,79; -5,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,09; -18,06</t>
+          <t>-42,78; -19,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 45,99</t>
+          <t>-2,54; 47,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 14,16</t>
+          <t>-26,71; 11,09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 3,08</t>
+          <t>-7,29; 2,99</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 1,59</t>
+          <t>-9,0; 2,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,94</t>
+          <t>-7,45; 2,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 0,06</t>
+          <t>-11,03; 0,43</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 3,57</t>
+          <t>-8,07; 3,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 1,87</t>
+          <t>-9,88; 2,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 3,39</t>
+          <t>-8,24; 2,97</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 0,07</t>
+          <t>-12,17; 0,42</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,53</t>
+          <t>2,6; 7,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,3</t>
+          <t>2,63; 7,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -10,75</t>
+          <t>-19,35; -10,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-21,44; -12,55</t>
+          <t>-21,35; -12,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,05</t>
+          <t>1,2; 7,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,35</t>
+          <t>0,47; 6,35</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>33,17; 115,13</t>
+          <t>30,6; 110,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>29,57; 111,28</t>
+          <t>29,36; 108,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,26; -13,18</t>
+          <t>-23,06; -13,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,23; -15,61</t>
+          <t>-25,2; -15,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,76; 24,28</t>
+          <t>4,12; 25,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,81; 22,25</t>
+          <t>1,41; 21,9</t>
         </is>
       </c>
     </row>
